--- a/packages.xlsx
+++ b/packages.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFCCCC"/>
-        <bgColor rgb="00FFCCCC"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,20 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="39" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="38" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,10 +479,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>Últ. Fecha Publicación</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Últ. Commit GitHub</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
@@ -498,17 +501,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pyodbc</t>
+          <t>pandas</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5.3.0</t>
+          <t>2.2.2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>BSD 3-Clause</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -523,12 +526,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>numpy, python-dateutil, pytz, tzdata</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>six</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -538,29 +541,39 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://github.com/mkleehammer/pyodbc</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>DB API module for ODBC</t>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://pandas.pydata.org</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Powerful data structures for data analysis, time series, and statistics</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pandas</t>
+          <t>numpy</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>2.4.2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -580,12 +593,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>numpy==2.4.1, python-dateutil==2.9.0.post0, tzdata==2025.3</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>six==1.17.0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -595,34 +608,44 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://pypi.org/project/pandas</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Powerful data structures for data analysis, time series, and statistics</t>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/numpy</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Fundamental package for array computing in Python</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>numpy</t>
+          <t>python-dateutil</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.4.1</t>
+          <t>2.9.0.post0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -637,7 +660,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>six</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -652,34 +675,44 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://pypi.org/project/numpy</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Fundamental package for array computing in Python</t>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://github.com/dateutil/dateutil</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Extensions to the standard Python datetime module</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>python-dateutil</t>
+          <t>six</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.9.0.post0</t>
+          <t>1.17.0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Apache</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -694,7 +727,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>six==1.17.0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -709,29 +742,39 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://github.com/dateutil/dateutil</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Extensions to the standard Python datetime module</t>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://github.com/benjaminp/six</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Python 2 and 3 compatibility utilities</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>six</t>
+          <t>pytz</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.17.0</t>
+          <t>2025.2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,17 +809,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://github.com/benjaminp/six</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Python 2 and 3 compatibility utilities</t>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>http://pythonhosted.org/pytz</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>World timezone definitions, modern and historical</t>
         </is>
       </c>
     </row>
@@ -828,126 +881,22 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>https://github.com/python/tzdata</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Provider of IANA time zone data</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>unidecode</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>1.4.0</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>GPL</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Licencia rechazada por política</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2025-04-24</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>https://pypi.org/project/unidecode</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>ASCII transliterations of Unicode text</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>pywin32</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>PSF</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Sin problemas detectados</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2025-07-14</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>https://pypi.org/project/pywin32</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Python for Window Extensions</t>
         </is>
       </c>
     </row>
